--- a/experiments/results/resnet34/CIFAR-100/ASH/adaptive/max/results.xlsx
+++ b/experiments/results/resnet34/CIFAR-100/ASH/adaptive/max/results.xlsx
@@ -353,7 +353,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O10"/>
+  <dimension ref="A1:O11"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col width="61.33203125" customWidth="1" style="3" min="15" max="15"/>
@@ -862,6 +862,55 @@
       <c r="O10" s="5" t="inlineStr">
         <is>
           <t>dice_p=None,ash_p=80,react_th=None,scale_th=5.0,type=max</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="5" t="n">
+        <v>7.66</v>
+      </c>
+      <c r="B11" s="5" t="n">
+        <v>98.39</v>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>84.14</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>72.75</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>53.03</v>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>88.93000000000001</v>
+      </c>
+      <c r="G11" s="5" t="n">
+        <v>35.39</v>
+      </c>
+      <c r="H11" s="5" t="n">
+        <v>92.48</v>
+      </c>
+      <c r="I11" s="5" t="n">
+        <v>12.69</v>
+      </c>
+      <c r="J11" s="5" t="n">
+        <v>97.63</v>
+      </c>
+      <c r="K11" s="5" t="n">
+        <v>56.71</v>
+      </c>
+      <c r="L11" s="5" t="n">
+        <v>87.94</v>
+      </c>
+      <c r="M11" s="5" t="n">
+        <v>41.6</v>
+      </c>
+      <c r="N11" s="5" t="n">
+        <v>89.69</v>
+      </c>
+      <c r="O11" s="5" t="inlineStr">
+        <is>
+          <t>dice_p=None,ash_p=80,react_th=None,scale_th=10.0,type=max</t>
         </is>
       </c>
     </row>
